--- a/output/graficos_dimensiones/comunal_d_depmen_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:07</t>
+    <t xml:space="preserve">2026-09-10 01:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:20</t>
+    <t xml:space="preserve">2026-09-12 22:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:32</t>
+    <t xml:space="preserve">2026-09-24 00:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
